--- a/data/trans_dic/P19-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 28,7</t>
+          <t>21,28; 28,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,22; 35,02</t>
+          <t>26,26; 35,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,84; 44,08</t>
+          <t>33,78; 43,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,57; 36,95</t>
+          <t>21,37; 36,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>35,91; 44,54</t>
+          <t>36,2; 44,62</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,35; 42,96</t>
+          <t>33,27; 42,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,18; 49,08</t>
+          <t>39,63; 48,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,67; 39,56</t>
+          <t>25,7; 39,28</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,26; 35,34</t>
+          <t>29,63; 35,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,83; 37,27</t>
+          <t>30,85; 37,06</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,1; 44,79</t>
+          <t>37,66; 44,71</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,79; 35,28</t>
+          <t>24,9; 35,93</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,06; 30,7</t>
+          <t>24,0; 30,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,94; 33,38</t>
+          <t>25,91; 32,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 39,12</t>
+          <t>31,16; 38,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,99; 37,72</t>
+          <t>25,72; 36,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,68; 37,37</t>
+          <t>29,8; 37,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,54; 37,45</t>
+          <t>30,26; 38,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,39; 46,22</t>
+          <t>38,68; 46,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>19,68; 36,49</t>
+          <t>18,97; 36,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,7; 32,7</t>
+          <t>27,38; 32,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,74; 33,97</t>
+          <t>28,99; 33,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,69; 41,45</t>
+          <t>35,64; 41,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,3; 34,28</t>
+          <t>22,83; 34,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,77; 29,72</t>
+          <t>22,27; 29,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,74; 29,52</t>
+          <t>22,55; 29,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,08; 32,45</t>
+          <t>25,18; 32,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,81; 32,21</t>
+          <t>24,08; 32,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,55; 36,55</t>
+          <t>29,54; 36,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,93; 37,96</t>
+          <t>30,85; 37,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,22; 39,7</t>
+          <t>32,38; 39,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,74; 42,85</t>
+          <t>35,87; 42,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,38; 32,36</t>
+          <t>27,16; 32,09</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,83; 32,81</t>
+          <t>27,5; 32,45</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,08; 35,22</t>
+          <t>29,53; 34,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,92; 36,1</t>
+          <t>30,74; 36,16</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,32; 31,32</t>
+          <t>23,27; 32,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,05; 29,56</t>
+          <t>22,6; 29,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,36; 34,18</t>
+          <t>26,51; 33,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,54; 31,0</t>
+          <t>9,29; 31,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,4; 41,75</t>
+          <t>33,13; 41,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 36,47</t>
+          <t>28,46; 36,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,06; 40,07</t>
+          <t>32,4; 40,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,5; 48,08</t>
+          <t>34,78; 48,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,33; 35,25</t>
+          <t>29,54; 35,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,69; 32,1</t>
+          <t>26,97; 32,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,41; 35,91</t>
+          <t>30,48; 35,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,03; 35,79</t>
+          <t>18,17; 35,7</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,35; 28,98</t>
+          <t>20,36; 29,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 25,13</t>
+          <t>16,77; 25,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,14; 32,25</t>
+          <t>22,94; 31,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,31; 29,33</t>
+          <t>22,27; 29,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,36; 34,47</t>
+          <t>25,26; 34,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,96; 31,8</t>
+          <t>23,31; 32,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,89; 35,71</t>
+          <t>26,91; 36,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,34; 37,78</t>
+          <t>31,35; 37,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,26; 30,3</t>
+          <t>24,2; 30,6</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,39; 27,47</t>
+          <t>21,4; 27,37</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,37; 32,69</t>
+          <t>26,38; 32,36</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,73; 32,48</t>
+          <t>27,88; 32,17</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,05; 26,23</t>
+          <t>16,54; 25,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,63; 23,08</t>
+          <t>13,5; 22,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,38; 24,22</t>
+          <t>15,49; 24,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,27; 30,87</t>
+          <t>23,02; 30,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,52; 26,45</t>
+          <t>17,8; 25,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,69; 31,73</t>
+          <t>21,76; 31,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,52; 34,61</t>
+          <t>25,51; 35,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,59; 26,75</t>
+          <t>6,77; 26,77</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,43; 24,5</t>
+          <t>18,7; 24,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18,97; 25,93</t>
+          <t>19,33; 25,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>21,87; 28,75</t>
+          <t>22,07; 28,87</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,08; 27,02</t>
+          <t>10,61; 26,94</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,36; 18,51</t>
+          <t>9,39; 19,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 13,0</t>
+          <t>5,98; 13,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,16; 17,59</t>
+          <t>10,3; 18,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,69; 18,13</t>
+          <t>11,71; 18,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,3; 18,28</t>
+          <t>10,27; 18,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,64; 16,74</t>
+          <t>9,66; 16,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 21,99</t>
+          <t>13,41; 22,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,35; 16,19</t>
+          <t>11,58; 16,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>11,08; 17,19</t>
+          <t>10,94; 16,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,0</t>
+          <t>8,79; 14,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,82; 19,25</t>
+          <t>13,18; 19,17</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,28; 16,48</t>
+          <t>12,32; 16,29</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,24; 26,34</t>
+          <t>23,38; 26,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,17; 26,08</t>
+          <t>23,24; 26,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,33; 30,59</t>
+          <t>27,52; 30,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18,92; 27,71</t>
+          <t>19,49; 27,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,8; 32,86</t>
+          <t>29,78; 33,02</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,85; 32,02</t>
+          <t>28,62; 31,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,89; 36,09</t>
+          <t>32,96; 36,15</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,2; 32,76</t>
+          <t>24,36; 32,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,03; 29,2</t>
+          <t>26,97; 29,31</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,49; 28,68</t>
+          <t>26,42; 28,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,55; 32,94</t>
+          <t>30,72; 33,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>24,28; 29,69</t>
+          <t>23,69; 29,62</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que en los últimos 6 meses han ido al dentista</t>
+          <t>Población que en los últimos 6 meses han ido al dentista (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>104615; 141806</t>
+          <t>105145; 141337</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>119099; 159041</t>
+          <t>119275; 158985</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141936; 184919</t>
+          <t>141688; 181901</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>81129; 145756</t>
+          <t>84285; 145853</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>167868; 208212</t>
+          <t>169236; 208606</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>143463; 184840</t>
+          <t>143132; 182757</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>155056; 194222</t>
+          <t>156853; 193314</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79833; 123026</t>
+          <t>79934; 122147</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>281314; 339844</t>
+          <t>284888; 341998</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>272667; 329619</t>
+          <t>272836; 327752</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310582; 365103</t>
+          <t>307005; 364465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>174882; 248861</t>
+          <t>175642; 253459</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>176932; 225817</t>
+          <t>176533; 224933</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>177900; 228987</t>
+          <t>177744; 225239</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>182771; 231031</t>
+          <t>184024; 228206</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>105422; 159167</t>
+          <t>108519; 153498</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>185651; 233744</t>
+          <t>186415; 231749</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>180286; 228551</t>
+          <t>184683; 233129</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>216351; 260472</t>
+          <t>218004; 262877</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100155; 185640</t>
+          <t>96531; 184686</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>377024; 445097</t>
+          <t>372689; 446755</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>372554; 440314</t>
+          <t>375809; 440636</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>411829; 478406</t>
+          <t>411262; 476440</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>216903; 319066</t>
+          <t>212455; 320732</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>145453; 189831</t>
+          <t>142214; 187146</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>155077; 201262</t>
+          <t>153770; 201312</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>167830; 217101</t>
+          <t>168485; 214919</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127155; 171971</t>
+          <t>128607; 171697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>203791; 252135</t>
+          <t>203760; 252004</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>219852; 269845</t>
+          <t>219294; 269724</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>213110; 262553</t>
+          <t>214160; 262071</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>192788; 231134</t>
+          <t>193505; 230848</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>363768; 429874</t>
+          <t>360852; 426257</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>387641; 456989</t>
+          <t>382965; 451903</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>400250; 468633</t>
+          <t>392893; 462883</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>331873; 387457</t>
+          <t>329916; 388145</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120828; 162298</t>
+          <t>120575; 167307</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135525; 181700</t>
+          <t>138891; 183182</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>170278; 220802</t>
+          <t>171272; 217897</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84478; 274564</t>
+          <t>82317; 275421</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>172199; 215292</t>
+          <t>170837; 215618</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>172397; 224387</t>
+          <t>175113; 224045</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>208090; 260108</t>
+          <t>210273; 260717</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>243909; 339922</t>
+          <t>245854; 340948</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>303258; 364419</t>
+          <t>305392; 367181</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>328265; 394742</t>
+          <t>331662; 395738</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>393859; 465106</t>
+          <t>394747; 465203</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>287235; 569973</t>
+          <t>289318; 568572</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>78686; 112082</t>
+          <t>78718; 112623</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>72297; 107557</t>
+          <t>71771; 107783</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>110601; 154147</t>
+          <t>109642; 152061</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124591; 163791</t>
+          <t>124382; 165950</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>102222; 138936</t>
+          <t>101825; 139007</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>102813; 142379</t>
+          <t>104385; 145256</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>133591; 177410</t>
+          <t>133711; 179256</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>168837; 203530</t>
+          <t>168880; 199443</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191624; 239310</t>
+          <t>191130; 241661</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187371; 240630</t>
+          <t>187404; 239722</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257094; 318700</t>
+          <t>257154; 315457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>304194; 356377</t>
+          <t>305867; 352947</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>49895; 76755</t>
+          <t>48387; 75504</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>42216; 71509</t>
+          <t>41833; 70837</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51419; 80959</t>
+          <t>51793; 82069</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84385; 111934</t>
+          <t>83495; 111289</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>60090; 90703</t>
+          <t>61052; 89115</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>76784; 112335</t>
+          <t>77043; 113001</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>96401; 130743</t>
+          <t>96354; 133710</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>46121; 162540</t>
+          <t>41146; 162682</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>117154; 155705</t>
+          <t>118850; 156420</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>125910; 172122</t>
+          <t>128291; 172546</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>155763; 204698</t>
+          <t>157127; 205551</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>107471; 262132</t>
+          <t>102907; 261379</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19651; 38843</t>
+          <t>19714; 40027</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>13842; 32492</t>
+          <t>14944; 32995</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26103; 45200</t>
+          <t>26479; 46262</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32669; 50634</t>
+          <t>32706; 51342</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34403; 61025</t>
+          <t>34276; 62944</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37501; 65101</t>
+          <t>37581; 65078</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53036; 87993</t>
+          <t>53664; 88207</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>47350; 67571</t>
+          <t>48322; 69260</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>60271; 93470</t>
+          <t>59510; 92090</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56653; 89407</t>
+          <t>56175; 89943</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>84266; 126476</t>
+          <t>86613; 125988</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>85546; 114819</t>
+          <t>85855; 113478</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>761136; 862782</t>
+          <t>765770; 869320</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>793371; 893185</t>
+          <t>795892; 897514</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927665; 1038411</t>
+          <t>934257; 1035721</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>650025; 952093</t>
+          <t>669893; 947806</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1006886; 1110122</t>
+          <t>1006060; 1115428</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1026159; 1139075</t>
+          <t>1018088; 1129440</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1165881; 1279347</t>
+          <t>1168344; 1281496</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>878391; 1189142</t>
+          <t>884215; 1187018</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1798612; 1942870</t>
+          <t>1794572; 1949930</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1849388; 2002245</t>
+          <t>1844792; 1998460</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2120052; 2285927</t>
+          <t>2131619; 2290065</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1715635; 2097718</t>
+          <t>1673995; 2093062</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 28,61</t>
+          <t>21,0; 28,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>26,26; 35,01</t>
+          <t>25,95; 35,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33,78; 43,37</t>
+          <t>34,06; 43,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,37; 36,97</t>
+          <t>20,99; 35,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,2; 44,62</t>
+          <t>36,18; 45,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,27; 42,48</t>
+          <t>33,19; 42,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,63; 48,85</t>
+          <t>39,16; 48,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,7; 39,28</t>
+          <t>24,67; 38,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>29,63; 35,57</t>
+          <t>29,54; 35,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,85; 37,06</t>
+          <t>30,76; 37,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,66; 44,71</t>
+          <t>38,06; 44,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,9; 35,93</t>
+          <t>24,55; 34,23</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,0; 30,58</t>
+          <t>23,66; 30,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>25,91; 32,84</t>
+          <t>26,46; 33,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,16; 38,65</t>
+          <t>31,03; 39,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,72; 36,38</t>
+          <t>23,06; 34,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>29,8; 37,05</t>
+          <t>29,58; 37,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 38,2</t>
+          <t>29,63; 37,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,68; 46,65</t>
+          <t>38,18; 46,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,97; 36,3</t>
+          <t>28,32; 37,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,38; 32,83</t>
+          <t>27,57; 32,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28,99; 33,99</t>
+          <t>28,66; 34,13</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,64; 41,28</t>
+          <t>35,74; 41,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,83; 34,46</t>
+          <t>27,27; 34,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>38,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,35%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22,27; 29,3</t>
+          <t>22,65; 29,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22,55; 29,52</t>
+          <t>22,3; 29,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,18; 32,12</t>
+          <t>25,03; 32,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,08; 32,15</t>
+          <t>22,86; 30,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,54; 36,54</t>
+          <t>29,35; 36,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,85; 37,94</t>
+          <t>30,43; 37,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,38; 39,62</t>
+          <t>32,48; 39,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,87; 42,8</t>
+          <t>34,98; 41,73</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,16; 32,09</t>
+          <t>27,1; 32,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27,5; 32,45</t>
+          <t>27,68; 32,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29,53; 34,79</t>
+          <t>29,94; 34,97</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>30,74; 36,16</t>
+          <t>30,05; 35,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,27; 32,28</t>
+          <t>23,25; 31,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>22,6; 29,8</t>
+          <t>22,73; 30,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,51; 33,73</t>
+          <t>26,28; 34,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 31,1</t>
+          <t>25,7; 32,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,13; 41,82</t>
+          <t>33,04; 41,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 36,42</t>
+          <t>28,31; 36,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,4; 40,17</t>
+          <t>32,55; 39,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>34,78; 48,23</t>
+          <t>32,52; 38,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>29,54; 35,51</t>
+          <t>29,26; 35,33</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26,97; 32,18</t>
+          <t>26,5; 32,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30,48; 35,92</t>
+          <t>30,47; 35,92</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,17; 35,7</t>
+          <t>30,11; 34,75</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,04%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,36; 29,12</t>
+          <t>20,01; 28,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,77; 25,18</t>
+          <t>16,58; 25,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,94; 31,82</t>
+          <t>22,86; 31,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22,27; 29,72</t>
+          <t>22,73; 29,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,26; 34,49</t>
+          <t>25,37; 34,29</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,31; 32,44</t>
+          <t>23,06; 32,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,91; 36,08</t>
+          <t>26,97; 35,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>31,35; 37,03</t>
+          <t>31,49; 37,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,2; 30,6</t>
+          <t>24,12; 30,3</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 27,37</t>
+          <t>21,53; 27,53</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,38; 32,36</t>
+          <t>26,27; 32,34</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>27,88; 32,17</t>
+          <t>27,81; 32,44</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,54; 25,81</t>
+          <t>16,81; 26,26</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13,5; 22,87</t>
+          <t>13,94; 23,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,49; 24,55</t>
+          <t>15,71; 24,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23,02; 30,69</t>
+          <t>22,72; 30,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,8; 25,99</t>
+          <t>18,2; 26,42</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,76; 31,92</t>
+          <t>21,77; 31,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,51; 35,4</t>
+          <t>25,56; 35,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,77; 26,77</t>
+          <t>23,18; 29,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,7; 24,61</t>
+          <t>18,35; 24,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19,33; 25,99</t>
+          <t>18,86; 26,25</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>22,07; 28,87</t>
+          <t>21,86; 28,48</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,61; 26,94</t>
+          <t>23,91; 28,62</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,45%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9,39; 19,07</t>
+          <t>9,65; 18,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,98; 13,21</t>
+          <t>6,08; 13,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,3; 18,0</t>
+          <t>10,18; 17,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11,71; 18,38</t>
+          <t>12,06; 19,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,27; 18,85</t>
+          <t>10,25; 18,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,66; 16,73</t>
+          <t>10,05; 17,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,41; 22,04</t>
+          <t>13,21; 21,72</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,58; 16,59</t>
+          <t>11,63; 16,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,93</t>
+          <t>10,92; 17,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 14,08</t>
+          <t>8,99; 14,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,18; 19,17</t>
+          <t>12,82; 19,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 16,29</t>
+          <t>12,48; 16,52</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>23,38; 26,54</t>
+          <t>23,42; 26,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23,24; 26,21</t>
+          <t>23,19; 26,29</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,52; 30,51</t>
+          <t>27,66; 30,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19,49; 27,58</t>
+          <t>24,69; 27,92</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,78; 33,02</t>
+          <t>29,83; 33,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,62; 31,75</t>
+          <t>28,65; 31,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>32,96; 36,15</t>
+          <t>32,94; 36,2</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>24,36; 32,7</t>
+          <t>29,9; 32,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>26,97; 29,31</t>
+          <t>27,15; 29,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26,42; 28,62</t>
+          <t>26,45; 28,67</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30,72; 33,0</t>
+          <t>30,69; 33,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>23,69; 29,62</t>
+          <t>27,74; 29,88</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111031</t>
+          <t>110207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>100805</t>
+          <t>112321</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>211836</t>
+          <t>222528</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>105145; 141337</t>
+          <t>103749; 141012</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>119275; 158985</t>
+          <t>117861; 159522</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>141688; 181901</t>
+          <t>142870; 181647</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84285; 145853</t>
+          <t>84483; 141473</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>169236; 208606</t>
+          <t>169145; 210620</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>143132; 182757</t>
+          <t>142795; 183502</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>156853; 193314</t>
+          <t>154977; 193618</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>79934; 122147</t>
+          <t>88867; 137383</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>284888; 341998</t>
+          <t>284023; 339248</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>272836; 327752</t>
+          <t>272039; 331990</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>307005; 364465</t>
+          <t>310292; 366577</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>175642; 253459</t>
+          <t>187305; 261149</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130255</t>
+          <t>134394</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>151201</t>
+          <t>162496</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>281456</t>
+          <t>296890</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>176533; 224933</t>
+          <t>174047; 223794</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>177744; 225239</t>
+          <t>181508; 229594</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>184024; 228206</t>
+          <t>183212; 232146</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>108519; 153498</t>
+          <t>109572; 162605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>186415; 231749</t>
+          <t>185001; 236272</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>184683; 233129</t>
+          <t>180805; 228574</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>218004; 262877</t>
+          <t>215152; 261773</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96531; 184686</t>
+          <t>140475; 185898</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>372689; 446755</t>
+          <t>375183; 443339</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>375809; 440636</t>
+          <t>371546; 442405</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>411262; 476440</t>
+          <t>412433; 477952</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>212455; 320732</t>
+          <t>264799; 330292</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148397</t>
+          <t>163656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>210974</t>
+          <t>236163</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>359371</t>
+          <t>399819</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>142214; 187146</t>
+          <t>144658; 191241</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>153770; 201312</t>
+          <t>152051; 199515</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>168485; 214919</t>
+          <t>167499; 216022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128607; 171697</t>
+          <t>141158; 189562</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>203760; 252004</t>
+          <t>202412; 253402</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>219294; 269724</t>
+          <t>216347; 268433</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>214160; 262071</t>
+          <t>214847; 263882</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>193505; 230848</t>
+          <t>216313; 258090</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>360852; 426257</t>
+          <t>359973; 426505</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>382965; 451903</t>
+          <t>385478; 455316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>392893; 462883</t>
+          <t>398304; 465296</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>329916; 388145</t>
+          <t>371376; 434139</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>190037</t>
+          <t>204288</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>274643</t>
+          <t>257937</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>464679</t>
+          <t>462224</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>120575; 167307</t>
+          <t>120479; 162685</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138891; 183182</t>
+          <t>139721; 184870</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171272; 217897</t>
+          <t>169790; 223148</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>82317; 275421</t>
+          <t>179486; 228393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>170837; 215618</t>
+          <t>170379; 215922</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>175113; 224045</t>
+          <t>174172; 223971</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>210273; 260717</t>
+          <t>211274; 259220</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>245854; 340948</t>
+          <t>237634; 278899</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305392; 367181</t>
+          <t>302490; 365268</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>331662; 395738</t>
+          <t>325899; 394433</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>394747; 465203</t>
+          <t>394609; 465201</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>289318; 568572</t>
+          <t>430364; 496651</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144784</t>
+          <t>156891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>185064</t>
+          <t>205588</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>329848</t>
+          <t>362479</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>78718; 112623</t>
+          <t>77399; 111206</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>71771; 107783</t>
+          <t>70969; 107198</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109642; 152061</t>
+          <t>109268; 151853</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>124382; 165950</t>
+          <t>137862; 178813</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>101825; 139007</t>
+          <t>102249; 138229</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>104385; 145256</t>
+          <t>103268; 144338</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>133711; 179256</t>
+          <t>133995; 177304</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>168880; 199443</t>
+          <t>189030; 223184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191130; 241661</t>
+          <t>190518; 239297</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187404; 239722</t>
+          <t>188590; 241121</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>257154; 315457</t>
+          <t>256091; 315282</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>305867; 352947</t>
+          <t>335558; 391486</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>96848</t>
+          <t>106944</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>103984</t>
+          <t>114144</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>200832</t>
+          <t>221089</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>48387; 75504</t>
+          <t>49194; 76823</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>41833; 70837</t>
+          <t>43193; 72352</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51793; 82069</t>
+          <t>52535; 81249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83495; 111289</t>
+          <t>91085; 122516</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>61052; 89115</t>
+          <t>62428; 90618</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>77043; 113001</t>
+          <t>77078; 111210</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>96354; 133710</t>
+          <t>96558; 133412</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>41146; 162682</t>
+          <t>101516; 127673</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>118850; 156420</t>
+          <t>116613; 157930</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>128291; 172546</t>
+          <t>125198; 174272</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>157127; 205551</t>
+          <t>155684; 202811</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>102907; 261379</t>
+          <t>200596; 240086</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>41361</t>
+          <t>46733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>57563</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98925</t>
+          <t>110016</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>19714; 40027</t>
+          <t>20245; 38696</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>14944; 32995</t>
+          <t>15190; 32925</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>26479; 46262</t>
+          <t>26168; 45365</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32706; 51342</t>
+          <t>36915; 58807</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>34276; 62944</t>
+          <t>34215; 61329</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37581; 65078</t>
+          <t>39087; 66532</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>53664; 88207</t>
+          <t>52855; 86930</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>48322; 69260</t>
+          <t>52965; 74992</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>59510; 92090</t>
+          <t>59404; 92845</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>56175; 89943</t>
+          <t>57429; 89672</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86613; 125988</t>
+          <t>84266; 125737</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>85855; 113478</t>
+          <t>95016; 125760</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>862713</t>
+          <t>923114</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1084234</t>
+          <t>1151931</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1946946</t>
+          <t>2075045</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>765770; 869320</t>
+          <t>767116; 869016</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>795892; 897514</t>
+          <t>793953; 900175</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>934257; 1035721</t>
+          <t>939015; 1038925</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>669893; 947806</t>
+          <t>865964; 978975</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1006060; 1115428</t>
+          <t>1007614; 1115681</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1018088; 1129440</t>
+          <t>1019104; 1132904</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1168344; 1281496</t>
+          <t>1167396; 1283111</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>884215; 1187018</t>
+          <t>1105992; 1205191</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1794572; 1949930</t>
+          <t>1806499; 1946168</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1844792; 1998460</t>
+          <t>1846546; 2001610</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2131619; 2290065</t>
+          <t>2129771; 2289983</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1673995; 2093062</t>
+          <t>1999274; 2152988</t>
         </is>
       </c>
     </row>
